--- a/mss_ai_ppt_sample_assets/backend/data/plus_data.xlsx
+++ b/mss_ai_ppt_sample_assets/backend/data/plus_data.xlsx
@@ -16,9 +16,6 @@
     <sheet name="告警表" sheetId="14" r:id="rId7"/>
     <sheet name="事件表" sheetId="6" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">暴露面!$A$1:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">资产漏洞表!$A$1:$W$9</definedName>
@@ -212,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="656">
   <si>
     <t>注：填充色为浅黄色的单元格需要手动查找数据填充，其余数据从MSSP平台导出底数据后覆盖子表内容，再更新单元格L1和M1自动按照统计周期计算结果；</t>
   </si>
@@ -232,7 +229,7 @@
     <t>TOP3的核心业务系统</t>
   </si>
   <si>
-    <t>系统1</t>
+    <t>手写</t>
   </si>
   <si>
     <t>威胁运营</t>
@@ -248,9 +245,6 @@
   </si>
   <si>
     <t>护网，可选，固定此格，来源提示词</t>
-  </si>
-  <si>
-    <t>系统2</t>
   </si>
   <si>
     <t>安全策略调优数量</t>
@@ -266,9 +260,6 @@
 中秋、国庆。元旦、春节、清明、五一、端午</t>
   </si>
   <si>
-    <t>系统3</t>
-  </si>
-  <si>
     <t>外部威胁告警数量</t>
   </si>
   <si>
@@ -342,9 +333,6 @@
   </si>
   <si>
     <t>前一服务周期被通报次数</t>
-  </si>
-  <si>
-    <t>手写</t>
   </si>
   <si>
     <t>通报风险应对</t>
@@ -1995,6 +1983,9 @@
     <t>内网</t>
   </si>
   <si>
+    <t>系统1</t>
+  </si>
+  <si>
     <t>服务器</t>
   </si>
   <si>
@@ -2029,6 +2020,9 @@
 tcpwrapped(64443)</t>
   </si>
   <si>
+    <t>系统2</t>
+  </si>
+  <si>
     <t>http(80)
 ssl(443,4480,23031,23020)
 ssh(22)
@@ -2045,6 +2039,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>系统3</t>
   </si>
   <si>
     <t>unknown(17561)
@@ -2924,7 +2921,7 @@
     <numFmt numFmtId="179" formatCode="0.00_ "/>
     <numFmt numFmtId="180" formatCode="0\.0,&quot;万&quot;"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="52">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3103,13 +3100,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="7" tint="0.8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="15"/>
       <color rgb="FFE1F9FE"/>
       <name val="OPPOSans-R"/>
@@ -3268,14 +3258,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3298,7 +3281,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3309,7 +3299,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="49">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3409,6 +3399,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4260,13 +4256,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="44" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="44" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4275,118 +4274,115 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="46" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="46" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="21" borderId="47" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="47" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="48" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="48" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="47" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="47" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="49" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="22" borderId="49" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="50" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="50" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="51" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="51" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4913,10 +4909,10 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4934,13 +4930,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -17435,194 +17431,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="可视化看板"/>
-      <sheetName val="数据统计"/>
-      <sheetName val="运营机制"/>
-      <sheetName val="资产表"/>
-      <sheetName val="暴露面"/>
-      <sheetName val="资产漏洞表"/>
-      <sheetName val="告警表"/>
-      <sheetName val="事件表"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>说明：
-事件类型：一般威胁、重大威胁、一般事件、重大事件标签取平台导出的，补充类型名称即可；
-设备离线类标签定义为业务连续性风险；
-未公开威胁类标签定义为最新威胁。</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>事件类型</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>事件创建时间</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>业务连续性风险</v>
-          </cell>
-          <cell r="B3">
-            <v>45891.3874421296</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>业务连续性风险</v>
-          </cell>
-          <cell r="B4">
-            <v>45943.9592592593</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>重大事件</v>
-          </cell>
-          <cell r="B5">
-            <v>45947.364375</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>重大事件</v>
-          </cell>
-          <cell r="B6">
-            <v>45973.5874768519</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>重大事件</v>
-          </cell>
-          <cell r="B7">
-            <v>46076.7486689815</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>重大事件</v>
-          </cell>
-          <cell r="B8">
-            <v>46077.6402662037</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>重大威胁</v>
-          </cell>
-          <cell r="B9">
-            <v>45985.3865509259</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>重大威胁</v>
-          </cell>
-          <cell r="B10">
-            <v>45880.4008564815</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>重大威胁</v>
-          </cell>
-          <cell r="B11">
-            <v>45958.7312037037</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>一般事件</v>
-          </cell>
-          <cell r="B12">
-            <v>45870.6352777778</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>一般事件</v>
-          </cell>
-          <cell r="B13">
-            <v>45871.5828819444</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>最新威胁</v>
-          </cell>
-          <cell r="B14">
-            <v>46059.4420949074</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>最新威胁</v>
-          </cell>
-          <cell r="B15">
-            <v>46059.6016087963</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>最新威胁</v>
-          </cell>
-          <cell r="B16">
-            <v>46079.6532638889</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>最新威胁</v>
-          </cell>
-          <cell r="B17">
-            <v>46086.4138657407</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>一般事件</v>
-          </cell>
-          <cell r="B18">
-            <v>46090.5363888889</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>最新威胁</v>
-          </cell>
-          <cell r="B19">
-            <v>46091.6809953704</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>最新威胁</v>
-          </cell>
-          <cell r="B20">
-            <v>46094.6038888889</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -19551,7 +19359,7 @@
       </c>
       <c r="I1" s="115">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
@@ -19598,50 +19406,50 @@
       <c r="B4" s="122"/>
       <c r="C4" s="123"/>
       <c r="D4" s="119" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E4" s="124"/>
       <c r="F4" s="93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="119">
         <v>100</v>
       </c>
       <c r="L4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" t="s">
         <v>14</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" s="58" t="s">
         <v>15</v>
-      </c>
-      <c r="N4" s="58" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="2:14">
       <c r="B5" s="122"/>
       <c r="C5" s="125"/>
       <c r="D5" s="119" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E5" s="124"/>
       <c r="F5" s="93" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS(告警表!D:D,"*外部威胁*",告警表!Z:Z,"&gt;="&amp;L1,告警表!Z:Z,"&lt;="&amp;M1)</f>
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:14">
       <c r="B6" s="127"/>
       <c r="C6" s="93" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="126">
         <f>COUNTIFS(资产漏洞表!T:T,"&gt;="&amp;L1,资产漏洞表!T:T,"&lt;="&amp;M1)</f>
@@ -19649,7 +19457,7 @@
       </c>
       <c r="E6" s="124"/>
       <c r="F6" s="93" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G6" s="126">
         <f>AVERAGEIFS(事件表!BA:BA,事件表!BA:BA,"&lt;&gt;",事件表!A:A,"*威胁*")</f>
@@ -19660,18 +19468,18 @@
     </row>
     <row r="7" spans="2:14">
       <c r="B7" s="129" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="130" t="str">
         <f>D3</f>
-        <v>系统1</v>
-      </c>
-      <c r="D7" s="119">
-        <v>10</v>
+        <v>手写</v>
+      </c>
+      <c r="D7" s="119" t="s">
+        <v>6</v>
       </c>
       <c r="E7" s="124"/>
       <c r="F7" s="93" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" s="126">
         <f>COUNTIFS(事件表!A:A,"*事件*",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)</f>
@@ -19684,14 +19492,14 @@
       <c r="B8" s="131"/>
       <c r="C8" s="130" t="str">
         <f>D4</f>
-        <v>系统2</v>
-      </c>
-      <c r="D8" s="119">
-        <v>20</v>
+        <v>手写</v>
+      </c>
+      <c r="D8" s="119" t="s">
+        <v>6</v>
       </c>
       <c r="E8" s="124"/>
       <c r="F8" s="93" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G8" s="126">
         <f>AVERAGEIFS(事件表!BA:BA,事件表!BA:BA,"&lt;&gt;",事件表!AW:AW,"已通告",事件表!A:A,"*事件*")</f>
@@ -19704,14 +19512,14 @@
       <c r="B9" s="131"/>
       <c r="C9" s="130" t="str">
         <f>D5</f>
-        <v>系统3</v>
-      </c>
-      <c r="D9" s="119">
-        <v>30</v>
+        <v>手写</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>6</v>
       </c>
       <c r="E9" s="124"/>
       <c r="F9" s="93" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G9" s="132">
         <f>(COUNTIFS(事件表!A:A,"*事件*",事件表!I:I,"*已*",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)+COUNTIFS(事件表!A:A,"*事件*",事件表!I:I,"*不处置*",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1))/G7</f>
@@ -19723,11 +19531,11 @@
     <row r="10" ht="15" customHeight="1" spans="2:14">
       <c r="B10" s="133"/>
       <c r="C10" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="119"/>
+        <v>25</v>
+      </c>
+      <c r="D10" s="124"/>
       <c r="E10" s="135" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" s="136"/>
       <c r="G10" s="137"/>
@@ -19735,7 +19543,7 @@
     <row r="11" spans="2:14">
       <c r="B11" s="138"/>
       <c r="C11" s="134" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D11" s="126">
         <f>COUNTIFS(事件表!A:A,"最新威胁",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)</f>
@@ -19743,7 +19551,7 @@
       </c>
       <c r="E11" s="135"/>
       <c r="F11" s="93" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" s="126">
         <f>D6+D10+D12</f>
@@ -19753,19 +19561,19 @@
     <row r="12" ht="16" customHeight="1" spans="2:14">
       <c r="B12" s="138"/>
       <c r="C12" s="134" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D12" s="119">
         <v>15</v>
       </c>
       <c r="E12" s="135" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F12" s="93" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G12" s="126">
-        <f>COUNTIFS([1]事件表!A:A,"*事件*",[1]事件表!B:B,"&gt;="&amp;L1,[1]事件表!B:B,"&lt;="&amp;M1)+COUNTIFS([1]事件表!A:A,"重大威胁",[1]事件表!B:B,"&gt;="&amp;L1,[1]事件表!B:B,"&lt;="&amp;M1)+COUNTIFS([1]事件表!A:A,"一般威胁",[1]事件表!B:B,"&gt;="&amp;L1,[1]事件表!B:B,"&lt;="&amp;M1)</f>
+        <f>COUNTIFS(事件表!A:A,"*事件*",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)+COUNTIFS(事件表!A:A,"重大威胁",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)+COUNTIFS(事件表!A:A,"一般威胁",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)</f>
         <v>10</v>
       </c>
     </row>
@@ -19780,7 +19588,7 @@
     <row r="14" spans="2:14">
       <c r="B14" s="138"/>
       <c r="C14" s="134" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="126">
         <f>D15+D16+D17</f>
@@ -19793,13 +19601,13 @@
     <row r="15" ht="18" customHeight="1" spans="2:14">
       <c r="B15" s="138"/>
       <c r="C15" s="134" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="119">
         <v>15</v>
       </c>
       <c r="E15" s="135" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F15" s="136"/>
       <c r="G15" s="137"/>
@@ -19807,7 +19615,7 @@
     <row r="16" spans="2:14">
       <c r="B16" s="138"/>
       <c r="C16" s="134" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="126">
         <f>COUNTIFS(资产漏洞表!P:P,"已防护")</f>
@@ -19820,7 +19628,7 @@
     <row r="17" spans="2:7">
       <c r="B17" s="138"/>
       <c r="C17" s="134" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" s="126">
         <f>COUNTIFS(资产漏洞表!P:P,"已修复")</f>
@@ -19832,13 +19640,13 @@
     <row r="18" spans="2:7">
       <c r="B18" s="139"/>
       <c r="C18" s="134" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" s="119">
         <v>1</v>
       </c>
       <c r="E18" s="140" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F18" s="141"/>
       <c r="G18" s="142"/>
@@ -19848,28 +19656,30 @@
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="144" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="93" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D20" s="119" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="E20" s="136" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F20" s="136"/>
       <c r="G20" s="136"/>
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="145" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C21" s="93" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="119"/>
+        <v>42</v>
+      </c>
+      <c r="D21" s="119">
+        <v>1200</v>
+      </c>
       <c r="E21" s="136"/>
       <c r="F21" s="136"/>
       <c r="G21" s="136"/>
@@ -19877,13 +19687,13 @@
     <row r="22" spans="2:7">
       <c r="B22" s="145"/>
       <c r="C22" s="93" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D22" s="119" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="E22" s="136" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F22" s="136"/>
       <c r="G22" s="136"/>
@@ -19891,7 +19701,7 @@
     <row r="23" spans="2:7">
       <c r="B23" s="145"/>
       <c r="C23" s="93" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D23" s="146">
         <f>COUNTIFS(资产漏洞表!P:P,"已修复")</f>
@@ -19904,7 +19714,7 @@
     <row r="24" spans="2:7">
       <c r="B24" s="145"/>
       <c r="C24" s="93" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D24" s="146">
         <f>COUNTIFS(资产漏洞表!P:P,"已防护")</f>
@@ -19917,13 +19727,13 @@
     <row r="25" spans="2:7">
       <c r="B25" s="147"/>
       <c r="C25" s="93" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D25" s="119" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="E25" s="136" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F25" s="136"/>
       <c r="G25" s="136"/>
@@ -19934,57 +19744,57 @@
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="144" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C27" s="93" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D27" s="119">
         <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="2:7">
       <c r="B28" s="145" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C28" s="93" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D28" s="119">
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="145"/>
       <c r="C29" s="93" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D29" s="119">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="147"/>
       <c r="C30" s="93" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D30" s="149">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -19993,31 +19803,31 @@
     </row>
     <row r="32" spans="2:7">
       <c r="B32" s="144" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C32" s="93" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D32" s="119" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="2:14">
       <c r="B33" s="145"/>
       <c r="C33" s="93" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D33" s="149">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="2:14">
       <c r="B34" s="145"/>
       <c r="C34" s="93" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D34" s="146">
         <f>COUNTIFS(资产漏洞表!E:E,"高危",资产漏洞表!P:P,"已防护")/COUNTIFS(资产漏洞表!E:E,"高危")</f>
@@ -20027,7 +19837,7 @@
     <row r="35" spans="2:14">
       <c r="B35" s="145"/>
       <c r="C35" s="93" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D35" s="146">
         <f>AVERAGEIFS(事件表!AZ:AZ,事件表!AZ:AZ,"&lt;&gt;",事件表!AW:AW,"已通告",事件表!A:A,"*事件*")</f>
@@ -20037,7 +19847,7 @@
     <row r="36" spans="2:14">
       <c r="B36" s="145"/>
       <c r="C36" s="93" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D36" s="146">
         <f>AVERAGEIFS(事件表!BA:BA,事件表!BA:BA,"&lt;&gt;",事件表!AW:AW,"已通告",事件表!A:A,"*事件*")</f>
@@ -20047,7 +19857,7 @@
     <row r="37" spans="2:14">
       <c r="B37" s="145"/>
       <c r="C37" s="93" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D37" s="146">
         <f>COUNTIFS(资产漏洞表!P:P,"*已*")</f>
@@ -20057,7 +19867,7 @@
     <row r="38" spans="2:14">
       <c r="B38" s="145"/>
       <c r="C38" s="93" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D38" s="146">
         <f>COUNTIFS(事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)</f>
@@ -20067,9 +19877,11 @@
     <row r="39" spans="2:14">
       <c r="B39" s="147"/>
       <c r="C39" s="93" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="119"/>
+        <v>64</v>
+      </c>
+      <c r="D39" s="119" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="40" spans="2:14">
       <c r="B40" s="143"/>
@@ -20103,19 +19915,19 @@
     </row>
     <row r="48" spans="2:14">
       <c r="B48" s="114" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="126" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="126" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="126" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" s="126" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="93" t="s">
-        <v>71</v>
-      </c>
       <c r="F48" s="126" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G48" s="151"/>
       <c r="H48" s="120"/>
@@ -20164,20 +19976,20 @@
     </row>
     <row r="51" spans="2:14">
       <c r="B51" s="114" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C51" s="156" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D51" s="126">
         <f>COUNTIFS(事件表!C:C,C51,事件表!A:A,"*事件*")</f>
         <v>2</v>
       </c>
       <c r="E51" s="114" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F51" s="126" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G51" s="157">
         <f>AVERAGEIFS(事件表!AZ:AZ,事件表!AZ:AZ,"&lt;&gt;",事件表!AW:AW,"已通告",事件表!A:A,"*事件*")</f>
@@ -20194,7 +20006,7 @@
     <row r="52" spans="2:14">
       <c r="B52" s="114"/>
       <c r="C52" s="158" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D52" s="126">
         <f>COUNTIFS(事件表!C:C,C52,事件表!A:A,"*事件*")</f>
@@ -20202,7 +20014,7 @@
       </c>
       <c r="E52" s="114"/>
       <c r="F52" s="126" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G52" s="157">
         <f>AVERAGEIFS(事件表!BA:BA,事件表!BA:BA,"&lt;&gt;",事件表!AW:AW,"已通告",事件表!A:A,"*事件*")</f>
@@ -20219,7 +20031,7 @@
     <row r="53" spans="2:14">
       <c r="B53" s="114"/>
       <c r="C53" s="158" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D53" s="126">
         <f>COUNTIFS(事件表!C:C,C53,事件表!A:A,"*事件*")</f>
@@ -20227,7 +20039,7 @@
       </c>
       <c r="E53" s="114"/>
       <c r="F53" s="126" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G53" s="157">
         <f>AVERAGEIFS(事件表!BB:BB,事件表!BB:BB,"&lt;&gt;",事件表!AW:AW,"已通告",事件表!A:A,"*事件*")</f>
@@ -20244,7 +20056,7 @@
     <row r="54" spans="2:14">
       <c r="B54" s="114"/>
       <c r="C54" s="158" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D54" s="126">
         <f>COUNTIFS(事件表!C:C,C54,事件表!A:A,"*事件*")</f>
@@ -20252,7 +20064,7 @@
       </c>
       <c r="E54" s="114"/>
       <c r="F54" s="126" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G54" s="157">
         <f>AVERAGEIFS(事件表!BC:BC,事件表!BC:BC,"&lt;&gt;",事件表!AW:AW,"已通告",事件表!A:A,"*事件*")</f>
@@ -20269,7 +20081,7 @@
     <row r="55" spans="2:14">
       <c r="B55" s="114"/>
       <c r="C55" s="158" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D55" s="126">
         <f>COUNTIFS(事件表!C:C,C55,事件表!A:A,"*事件*")</f>
@@ -20277,7 +20089,7 @@
       </c>
       <c r="E55" s="114"/>
       <c r="F55" s="126" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G55" s="157">
         <f>AVERAGEIFS(事件表!BD:BD,事件表!BD:BD,"&lt;&gt;",事件表!AW:AW,"已通告",事件表!A:A,"*事件*")</f>
@@ -20303,7 +20115,7 @@
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="93" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C57" s="93"/>
       <c r="D57" s="93"/>
@@ -20320,7 +20132,7 @@
     </row>
     <row r="58" spans="2:14">
       <c r="B58" s="93" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C58" s="126" t="str">
         <f>TEXT(L1,"YYYY-MM")</f>
@@ -20373,7 +20185,7 @@
     </row>
     <row r="59" spans="2:14">
       <c r="B59" s="93" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C59" s="153">
         <f>AVERAGEIFS(事件表!BA:BA,事件表!$B:$B,"&gt;="&amp;DATE(YEAR(C58),MONTH(C58),1),事件表!$B:$B,"&lt;="&amp;DATE(YEAR(C58),MONTH(C58),DAY(EOMONTH(C58,0))))</f>
@@ -20428,64 +20240,64 @@
     </row>
     <row r="61" ht="30" customHeight="1" spans="2:14">
       <c r="B61" s="126" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C61" s="93" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D61" s="161">
         <v>65545</v>
       </c>
       <c r="E61" s="151"/>
       <c r="F61" s="162" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G61" s="163" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H61" s="164"/>
       <c r="I61" s="162" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J61" s="163" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K61" s="164"/>
       <c r="L61" s="162" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M61" s="165" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N61" s="152"/>
     </row>
     <row r="62" ht="27" customHeight="1" spans="2:14">
       <c r="B62" s="126" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C62" s="93" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D62" s="126">
         <f>COUNTIFS(告警表!D:D,"*威胁*")</f>
         <v>5</v>
       </c>
       <c r="F62" s="166" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G62" s="167">
         <v>2064</v>
       </c>
       <c r="H62" s="168"/>
       <c r="I62" s="166" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J62" s="167">
         <v>1254</v>
       </c>
       <c r="K62" s="168"/>
       <c r="L62" s="169" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M62" s="170">
         <v>2684</v>
@@ -20495,28 +20307,28 @@
     <row r="63" ht="27" customHeight="1" spans="2:14">
       <c r="B63" s="126"/>
       <c r="C63" s="93" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D63" s="126">
         <f>COUNTIFS(事件表!A:A,"重大威胁",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)+COUNTIFS(事件表!A:A,"一般威胁",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)</f>
         <v>3</v>
       </c>
       <c r="F63" s="166" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G63" s="167">
         <v>726</v>
       </c>
       <c r="H63" s="168"/>
       <c r="I63" s="166" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J63" s="167">
         <v>1242</v>
       </c>
       <c r="K63" s="168"/>
       <c r="L63" s="169" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M63" s="170">
         <v>2337</v>
@@ -20526,28 +20338,28 @@
     <row r="64" ht="27" customHeight="1" spans="2:14">
       <c r="B64" s="126"/>
       <c r="C64" s="93" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D64" s="126">
         <f>AVERAGEIFS(事件表!BA:BA,事件表!BA:BA,"&lt;&gt;",事件表!AW:AW,"已通告",事件表!A:A,"*威胁*")</f>
         <v>3.54</v>
       </c>
       <c r="F64" s="166" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G64" s="167">
         <v>582</v>
       </c>
       <c r="H64" s="168"/>
       <c r="I64" s="166" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J64" s="167">
         <v>735</v>
       </c>
       <c r="K64" s="168"/>
       <c r="L64" s="169" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M64" s="170">
         <v>204</v>
@@ -20556,30 +20368,30 @@
     </row>
     <row r="65" ht="27" customHeight="1" spans="1:14">
       <c r="B65" s="126" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C65" s="93" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D65" s="119">
         <v>2</v>
       </c>
       <c r="F65" s="166" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G65" s="167">
         <v>327</v>
       </c>
       <c r="H65" s="168"/>
       <c r="I65" s="162" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J65" s="163">
         <v>423</v>
       </c>
       <c r="K65" s="168"/>
       <c r="L65" s="169" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M65" s="170">
         <v>9</v>
@@ -20589,27 +20401,27 @@
     <row r="66" ht="27" customHeight="1" spans="1:14">
       <c r="B66" s="126"/>
       <c r="C66" s="93" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D66" s="119">
         <v>0</v>
       </c>
       <c r="F66" s="166" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G66" s="167">
         <v>259</v>
       </c>
       <c r="H66" s="168"/>
       <c r="I66" s="166" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J66" s="167">
         <v>341</v>
       </c>
       <c r="K66" s="168"/>
       <c r="L66" s="169" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M66" s="170">
         <v>7</v>
@@ -20618,24 +20430,24 @@
     </row>
     <row r="67" ht="27" customHeight="1" spans="1:14">
       <c r="B67" s="126" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C67" s="93" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D67" s="126">
         <f>COUNTIFS(事件表!A:A,"最新威胁",事件表!B:B,"&gt;="&amp;L1,事件表!B:B,"&lt;="&amp;M1)</f>
         <v>6</v>
       </c>
       <c r="F67" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="N67" s="137"/>
     </row>
     <row r="68" ht="27" customHeight="1" spans="1:14">
       <c r="B68" s="126"/>
       <c r="C68" s="93" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D68" s="119">
         <v>15</v>
@@ -20648,7 +20460,7 @@
     </row>
     <row r="70" spans="1:14">
       <c r="B70" s="171" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C70" s="172"/>
       <c r="D70" s="172"/>
@@ -20716,10 +20528,10 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B72" s="121" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C72" s="161">
         <v>6729</v>
@@ -20752,10 +20564,10 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B73" s="121" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C73" s="161">
         <v>145428</v>
@@ -20788,7 +20600,7 @@
     </row>
     <row r="74" spans="1:14">
       <c r="B74" s="121" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C74" s="161">
         <v>303457</v>
@@ -20829,7 +20641,7 @@
     </row>
     <row r="75" spans="1:14">
       <c r="B75" s="121" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C75" s="126">
         <f>COUNTIFS(告警表!$Z:$Z,"&gt;="&amp;DATE(YEAR(C71),MONTH(C71),1),告警表!$Z:$Z,"&lt;="&amp;DATE(YEAR(C71),MONTH(C71),DAY(EOMONTH(C71,0))))</f>
@@ -20882,7 +20694,7 @@
     </row>
     <row r="76" spans="1:14">
       <c r="B76" s="121" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C76" s="126">
         <f>COUNTIFS(事件表!A:A,"*事件*",事件表!$B:$B,"&gt;="&amp;DATE(YEAR(C71),MONTH(C71),1),事件表!$B:$B,"&lt;="&amp;DATE(YEAR(C71),MONTH(C71),DAY(EOMONTH(C71,0))))</f>
@@ -20935,7 +20747,7 @@
     </row>
     <row r="77" spans="1:14">
       <c r="B77" s="121" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C77" s="119">
         <v>40</v>
@@ -20971,30 +20783,30 @@
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:14">
       <c r="B79" s="126" t="s">
+        <v>126</v>
+      </c>
+      <c r="C79" s="126" t="s">
+        <v>127</v>
+      </c>
+      <c r="D79" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="E79" s="126" t="s">
         <v>129</v>
       </c>
-      <c r="C79" s="126" t="s">
+      <c r="F79" s="126" t="s">
         <v>130</v>
-      </c>
-      <c r="D79" s="114" t="s">
-        <v>131</v>
-      </c>
-      <c r="E79" s="126" t="s">
-        <v>132</v>
-      </c>
-      <c r="F79" s="126" t="s">
-        <v>133</v>
       </c>
       <c r="G79" s="151"/>
       <c r="H79" s="93" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I79" s="126">
         <f>暴露面!E4</f>
         <v>3</v>
       </c>
       <c r="J79" s="93" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K79" s="126">
         <f>COUNTIFS(资产表!F:F,"服务器",资产表!AG:AG,"内网")</f>
@@ -21002,7 +20814,7 @@
       </c>
       <c r="L79" s="151"/>
       <c r="M79" s="93" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="N79" s="175"/>
     </row>
@@ -21016,7 +20828,7 @@
         <f>COUNTIFS(资产漏洞表!N:N,"外网",资产漏洞表!P:P,"*已*",资产漏洞表!T:T,"&gt;="&amp;L1,资产漏洞表!T:T,"&lt;="&amp;M1)</f>
         <v>0</v>
       </c>
-      <c r="E80" s="119">
+      <c r="E80" s="176">
         <v>62</v>
       </c>
       <c r="F80" s="154" t="e">
@@ -21024,14 +20836,14 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H80" s="93" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I80" s="126">
         <f>暴露面!E5</f>
         <v>27</v>
       </c>
       <c r="J80" s="93" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K80" s="126">
         <f>COUNTIFS(资产表!F:F,"服务器",资产表!AG:AG,"内网",资产表!E:E,"服务内")</f>
@@ -21040,17 +20852,19 @@
       <c r="N80" s="137"/>
     </row>
     <row r="81" spans="2:14">
-      <c r="B81" s="176"/>
+      <c r="B81" s="177"/>
       <c r="C81" s="136"/>
       <c r="D81" s="136"/>
       <c r="E81" s="136"/>
       <c r="F81" s="136"/>
       <c r="H81" s="93" t="s">
-        <v>139</v>
-      </c>
-      <c r="I81" s="177"/>
+        <v>136</v>
+      </c>
+      <c r="I81" s="119">
+        <v>10</v>
+      </c>
       <c r="J81" s="93" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K81" s="126">
         <f>COUNTIFS(资产漏洞表!N:N,"内网")</f>
@@ -21060,27 +20874,27 @@
     </row>
     <row r="82" spans="2:14">
       <c r="B82" s="126" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C82" s="178"/>
       <c r="D82" s="126" t="s">
+        <v>139</v>
+      </c>
+      <c r="E82" s="126" t="s">
+        <v>140</v>
+      </c>
+      <c r="F82" s="126" t="s">
+        <v>141</v>
+      </c>
+      <c r="H82" s="93" t="s">
         <v>142</v>
-      </c>
-      <c r="E82" s="126" t="s">
-        <v>143</v>
-      </c>
-      <c r="F82" s="126" t="s">
-        <v>144</v>
-      </c>
-      <c r="H82" s="93" t="s">
-        <v>145</v>
       </c>
       <c r="I82" s="126">
         <f>COUNTIFS(资产漏洞表!N:N,"外网")</f>
         <v>0</v>
       </c>
       <c r="J82" s="93" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K82" s="126">
         <f>COUNTIFS(资产漏洞表!N:N,"内网",资产漏洞表!P:P,"已防护")</f>
@@ -21091,7 +20905,7 @@
     <row r="83" spans="2:14">
       <c r="B83" s="126"/>
       <c r="C83" s="93" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D83" s="126">
         <f>COUNTIFS(资产漏洞表!E:E,"高危")</f>
@@ -21108,7 +20922,7 @@
       <c r="H83" s="93"/>
       <c r="I83" s="93"/>
       <c r="J83" s="93" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K83" s="126">
         <f>COUNTIFS(资产漏洞表!N:N,"内网",资产漏洞表!P:P,"已修复")</f>
@@ -21119,7 +20933,7 @@
     <row r="84" spans="2:14">
       <c r="B84" s="126"/>
       <c r="C84" s="93" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D84" s="126">
         <f>COUNTIFS(资产漏洞表!E:E,"中危")</f>
@@ -21138,7 +20952,7 @@
     <row r="85" spans="2:14">
       <c r="B85" s="126"/>
       <c r="C85" s="93" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D85" s="126">
         <f>COUNTIFS(资产漏洞表!E:E,"低危")</f>
@@ -21156,7 +20970,7 @@
     </row>
     <row r="86" spans="2:14">
       <c r="B86" s="126" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C86" s="126" t="str">
         <f>TEXT(L1,"YYYY-MM")</f>
@@ -21209,7 +21023,7 @@
     </row>
     <row r="87" spans="2:14">
       <c r="B87" s="126" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C87" s="126">
         <f>COUNTIFS(资产漏洞表!$T:$T,"&gt;="&amp;DATE(YEAR(C86),MONTH(C86),1),资产漏洞表!$T:$T,"&lt;="&amp;DATE(YEAR(C86),MONTH(C86),DAY(EOMONTH(C86,0))))</f>
@@ -21262,7 +21076,7 @@
     </row>
     <row r="88" spans="2:14">
       <c r="B88" s="126" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C88" s="126">
         <f>COUNTIFS(资产漏洞表!P:P,"*已*",资产漏洞表!$T:$T,"&gt;="&amp;DATE(YEAR(C86),MONTH(C86),1),资产漏洞表!$T:$T,"&lt;="&amp;DATE(YEAR(C86),MONTH(C86),DAY(EOMONTH(C86,0))))</f>
@@ -21315,38 +21129,38 @@
     </row>
     <row r="90" spans="2:14">
       <c r="B90" s="120" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C90" s="93" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D90" s="119">
         <v>4</v>
       </c>
       <c r="E90" s="129" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F90" s="93"/>
       <c r="G90" s="93" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H90" s="126" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="91" spans="2:14">
       <c r="B91" s="118" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C91" s="93" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D91" s="119">
         <v>0</v>
       </c>
       <c r="E91" s="131"/>
       <c r="F91" s="175" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G91" s="161">
         <v>9623</v>
@@ -21358,14 +21172,14 @@
     <row r="92" spans="2:14">
       <c r="B92" s="179"/>
       <c r="C92" s="93" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D92" s="149">
         <v>1</v>
       </c>
       <c r="E92" s="131"/>
       <c r="F92" s="175" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G92" s="161">
         <v>28655</v>
@@ -21380,7 +21194,7 @@
       <c r="D93" s="180"/>
       <c r="E93" s="131"/>
       <c r="F93" s="175" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G93" s="161">
         <v>3461</v>
@@ -21395,7 +21209,7 @@
       <c r="D94" s="180"/>
       <c r="E94" s="131"/>
       <c r="F94" s="175" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G94" s="161">
         <v>16440</v>
@@ -21483,7 +21297,7 @@
     <row r="1" ht="7.05" customHeight="1"/>
     <row r="2" ht="25.05" customHeight="1" spans="2:7">
       <c r="B2" s="48" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
@@ -21493,87 +21307,87 @@
     </row>
     <row r="3" ht="25.05" customHeight="1" spans="2:7">
       <c r="B3" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="F3" s="52" t="s">
         <v>166</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>168</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>169</v>
       </c>
       <c r="G3" s="53"/>
     </row>
     <row r="4" ht="28.8" spans="2:7">
       <c r="B4" s="54" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="F4" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>172</v>
-      </c>
-      <c r="E4" s="55" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="52" t="s">
-        <v>174</v>
       </c>
       <c r="G4" s="53"/>
     </row>
     <row r="5" ht="28.8" spans="2:7">
       <c r="B5" s="56"/>
       <c r="C5" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="52" t="s">
         <v>175</v>
-      </c>
-      <c r="D5" s="55" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="55" t="s">
-        <v>177</v>
-      </c>
-      <c r="F5" s="52" t="s">
-        <v>178</v>
       </c>
       <c r="G5" s="53"/>
     </row>
     <row r="6" ht="49.95" customHeight="1" spans="2:7">
       <c r="B6" s="57"/>
       <c r="C6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="52" t="s">
         <v>179</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="52" t="s">
-        <v>182</v>
       </c>
       <c r="G6" s="53"/>
     </row>
     <row r="7" ht="66" customHeight="1" spans="2:7">
       <c r="B7" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="59" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="55" t="s">
-        <v>185</v>
-      </c>
-      <c r="E7" s="55" t="s">
-        <v>186</v>
-      </c>
       <c r="F7" s="52" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G7" s="53"/>
     </row>
@@ -21581,29 +21395,29 @@
       <c r="B8" s="56"/>
       <c r="C8" s="60"/>
       <c r="D8" s="61" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G8" s="53"/>
     </row>
     <row r="9" ht="63" customHeight="1" spans="2:7">
       <c r="B9" s="56"/>
       <c r="C9" s="59" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G9" s="53"/>
     </row>
@@ -21611,63 +21425,63 @@
       <c r="B10" s="57"/>
       <c r="C10" s="60"/>
       <c r="D10" s="55" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G10" s="53"/>
     </row>
     <row r="11" ht="45" customHeight="1" spans="2:7">
       <c r="B11" s="54" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" s="55" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="52" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="55" t="s">
-        <v>194</v>
-      </c>
       <c r="F11" s="52" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G11" s="53"/>
     </row>
     <row r="12" ht="75" customHeight="1" spans="2:7">
       <c r="B12" s="56"/>
       <c r="C12" s="52" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G12" s="53"/>
     </row>
     <row r="13" ht="87" customHeight="1" spans="2:7">
       <c r="B13" s="56"/>
       <c r="C13" s="62" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D13" s="62" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E13" s="62" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F13" s="63" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G13" s="64"/>
     </row>
@@ -21684,55 +21498,55 @@
     <row r="15" ht="73.95" customHeight="1" spans="2:7">
       <c r="B15" s="51"/>
       <c r="C15" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="F15" s="52" t="s">
         <v>200</v>
-      </c>
-      <c r="D15" s="55" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="55" t="s">
-        <v>202</v>
-      </c>
-      <c r="F15" s="52" t="s">
-        <v>203</v>
       </c>
       <c r="G15" s="53"/>
     </row>
     <row r="16" ht="57.6" spans="2:7">
       <c r="B16" s="65"/>
       <c r="C16" s="63" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D16" s="62" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E16" s="62" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F16" s="63" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G16" s="64"/>
     </row>
     <row r="17" ht="58.05" customHeight="1" spans="2:14">
       <c r="B17" s="66"/>
       <c r="C17" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="F17" s="67" t="s">
         <v>206</v>
-      </c>
-      <c r="D17" s="68" t="s">
-        <v>207</v>
-      </c>
-      <c r="E17" s="68" t="s">
-        <v>208</v>
-      </c>
-      <c r="F17" s="67" t="s">
-        <v>209</v>
       </c>
       <c r="G17" s="69"/>
     </row>
     <row r="18" ht="25.05" customHeight="1"/>
     <row r="19" ht="34.05" customHeight="1" spans="2:14">
       <c r="B19" s="70" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
@@ -21743,7 +21557,7 @@
     </row>
     <row r="20" ht="82.95" customHeight="1" spans="2:14">
       <c r="B20" s="72" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C20" s="73"/>
       <c r="D20" s="73"/>
@@ -21752,7 +21566,7 @@
       <c r="G20" s="73"/>
       <c r="H20" s="73"/>
       <c r="J20" s="72" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K20" s="73"/>
       <c r="L20" s="73"/>
@@ -21761,202 +21575,202 @@
     </row>
     <row r="21" ht="25.95" customHeight="1" spans="2:14">
       <c r="B21" s="74" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="75" t="s">
+        <v>211</v>
+      </c>
+      <c r="D21" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" s="77" t="s">
         <v>213</v>
-      </c>
-      <c r="C21" s="75" t="s">
-        <v>214</v>
-      </c>
-      <c r="D21" s="76" t="s">
-        <v>215</v>
-      </c>
-      <c r="E21" s="77" t="s">
-        <v>216</v>
       </c>
       <c r="F21" s="78"/>
       <c r="G21" s="79"/>
       <c r="H21" s="80"/>
       <c r="J21" s="81" t="s">
+        <v>214</v>
+      </c>
+      <c r="K21" s="82" t="s">
+        <v>215</v>
+      </c>
+      <c r="L21" s="82" t="s">
+        <v>216</v>
+      </c>
+      <c r="M21" s="82" t="s">
         <v>217</v>
       </c>
-      <c r="K21" s="82" t="s">
+      <c r="N21" s="82" t="s">
         <v>218</v>
-      </c>
-      <c r="L21" s="82" t="s">
-        <v>219</v>
-      </c>
-      <c r="M21" s="82" t="s">
-        <v>220</v>
-      </c>
-      <c r="N21" s="82" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="22" ht="102" customHeight="1" spans="2:14">
       <c r="B22" s="83" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" s="84" t="s">
+        <v>220</v>
+      </c>
+      <c r="D22" s="85" t="s">
+        <v>221</v>
+      </c>
+      <c r="E22" s="86" t="s">
         <v>222</v>
-      </c>
-      <c r="C22" s="84" t="s">
-        <v>223</v>
-      </c>
-      <c r="D22" s="85" t="s">
-        <v>224</v>
-      </c>
-      <c r="E22" s="86" t="s">
-        <v>225</v>
       </c>
       <c r="F22" s="87"/>
       <c r="G22" s="88"/>
       <c r="H22" s="53"/>
       <c r="J22" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="K22" s="90" t="s">
+        <v>224</v>
+      </c>
+      <c r="L22" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="M22" s="92" t="s">
         <v>226</v>
       </c>
-      <c r="K22" s="90" t="s">
+      <c r="N22" s="93" t="s">
         <v>227</v>
-      </c>
-      <c r="L22" s="91" t="s">
-        <v>228</v>
-      </c>
-      <c r="M22" s="92" t="s">
-        <v>229</v>
-      </c>
-      <c r="N22" s="93" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="23" ht="101" customHeight="1" spans="2:14">
       <c r="B23" s="83"/>
       <c r="C23" s="84" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D23" s="85" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E23" s="94" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F23" s="95"/>
       <c r="G23" s="96"/>
       <c r="H23" s="53"/>
       <c r="J23" s="97" t="s">
+        <v>230</v>
+      </c>
+      <c r="K23" s="90" t="s">
+        <v>231</v>
+      </c>
+      <c r="L23" s="92" t="s">
+        <v>232</v>
+      </c>
+      <c r="M23" s="92" t="s">
         <v>233</v>
       </c>
-      <c r="K23" s="90" t="s">
-        <v>234</v>
-      </c>
-      <c r="L23" s="92" t="s">
-        <v>235</v>
-      </c>
-      <c r="M23" s="92" t="s">
-        <v>236</v>
-      </c>
       <c r="N23" s="93" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" ht="105" customHeight="1" spans="2:14">
       <c r="B24" s="83" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C24" s="98" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D24" s="86" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E24" s="86" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F24" s="95"/>
       <c r="G24" s="96"/>
       <c r="H24" s="53"/>
       <c r="J24" s="99" t="s">
+        <v>237</v>
+      </c>
+      <c r="K24" s="90" t="s">
+        <v>238</v>
+      </c>
+      <c r="L24" s="92" t="s">
+        <v>239</v>
+      </c>
+      <c r="M24" s="92" t="s">
         <v>240</v>
       </c>
-      <c r="K24" s="90" t="s">
+      <c r="N24" s="93" t="s">
         <v>241</v>
-      </c>
-      <c r="L24" s="92" t="s">
-        <v>242</v>
-      </c>
-      <c r="M24" s="92" t="s">
-        <v>243</v>
-      </c>
-      <c r="N24" s="93" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="25" ht="66" customHeight="1" spans="2:14">
       <c r="B25" s="83"/>
       <c r="C25" s="84" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D25" s="85" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E25" s="86" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F25" s="95"/>
       <c r="G25" s="96"/>
       <c r="H25" s="53"/>
       <c r="J25" s="100" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K25" s="90" t="s">
+        <v>245</v>
+      </c>
+      <c r="L25" s="92" t="s">
+        <v>246</v>
+      </c>
+      <c r="M25" s="92" t="s">
+        <v>247</v>
+      </c>
+      <c r="N25" s="93" t="s">
         <v>248</v>
-      </c>
-      <c r="L25" s="92" t="s">
-        <v>249</v>
-      </c>
-      <c r="M25" s="92" t="s">
-        <v>250</v>
-      </c>
-      <c r="N25" s="93" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="26" ht="51" customHeight="1" spans="2:14">
       <c r="B26" s="83" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C26" s="85" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D26" s="101" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E26" s="87" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F26" s="95"/>
       <c r="G26" s="96"/>
       <c r="H26" s="53"/>
       <c r="J26" s="102" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K26" s="90" t="s">
+        <v>252</v>
+      </c>
+      <c r="L26" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="M26" s="92" t="s">
+        <v>254</v>
+      </c>
+      <c r="N26" s="93" t="s">
         <v>255</v>
-      </c>
-      <c r="L26" s="92" t="s">
-        <v>256</v>
-      </c>
-      <c r="M26" s="92" t="s">
-        <v>257</v>
-      </c>
-      <c r="N26" s="93" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="27" ht="71" customHeight="1" spans="2:14">
       <c r="B27" s="83"/>
       <c r="C27" s="103" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D27" s="104" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E27" s="86" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F27" s="95"/>
       <c r="G27" s="96"/>
@@ -21964,16 +21778,16 @@
     </row>
     <row r="28" ht="55" customHeight="1" spans="2:14">
       <c r="B28" s="83" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C28" s="84" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D28" s="85" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E28" s="86" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F28" s="95"/>
       <c r="G28" s="96"/>
@@ -21982,13 +21796,13 @@
     <row r="29" ht="62" customHeight="1" spans="2:14">
       <c r="B29" s="105"/>
       <c r="C29" s="106" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D29" s="107" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E29" s="108" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F29" s="109"/>
       <c r="G29" s="110"/>
@@ -22044,36 +21858,36 @@
   <sheetData>
     <row r="1" s="30" customFormat="1" ht="18" customHeight="1" spans="1:6">
       <c r="A1" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1" s="46" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="E1" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="46" t="s">
         <v>267</v>
-      </c>
-      <c r="C1" s="46" t="s">
-        <v>268</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="E1" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="F1" s="46" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="2" s="30" customFormat="1" ht="18" customHeight="1" spans="1:6">
       <c r="A2" s="47" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E2" s="47">
         <v>1</v>
@@ -22087,7 +21901,7 @@
       <c r="B3" s="47"/>
       <c r="C3" s="47"/>
       <c r="D3" s="47" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E3" s="47">
         <v>7</v>
@@ -22100,10 +21914,10 @@
       <c r="A4" s="47"/>
       <c r="B4" s="47"/>
       <c r="C4" s="47" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E4" s="47">
         <v>3</v>
@@ -22116,10 +21930,10 @@
       <c r="A5" s="47"/>
       <c r="B5" s="47"/>
       <c r="C5" s="47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E5" s="47">
         <v>27</v>
@@ -22132,10 +21946,10 @@
       <c r="A6" s="47"/>
       <c r="B6" s="47"/>
       <c r="C6" s="47" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E6" s="47">
         <v>20</v>
@@ -22148,10 +21962,10 @@
       <c r="A7" s="47"/>
       <c r="B7" s="47"/>
       <c r="C7" s="47" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E7" s="47">
         <v>7</v>
@@ -22164,10 +21978,10 @@
       <c r="A8" s="47"/>
       <c r="B8" s="47"/>
       <c r="C8" s="47" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E8" s="47">
         <v>4</v>
@@ -22180,10 +21994,10 @@
       <c r="A9" s="47"/>
       <c r="B9" s="47"/>
       <c r="C9" s="47" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E9" s="47">
         <v>0</v>
@@ -22196,66 +22010,66 @@
       <c r="A10" s="47"/>
       <c r="B10" s="47"/>
       <c r="C10" s="47" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E10" s="47">
         <v>27</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" s="30" customFormat="1" ht="18" customHeight="1" spans="1:6">
       <c r="A11" s="47"/>
       <c r="B11" s="47" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E11" s="47">
         <v>0</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" s="30" customFormat="1" ht="18" customHeight="1" spans="1:6">
       <c r="A12" s="47"/>
       <c r="B12" s="47"/>
       <c r="C12" s="47" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E12" s="47">
         <v>0</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" s="30" customFormat="1" ht="18" customHeight="1" spans="1:6">
       <c r="A13" s="47"/>
       <c r="B13" s="47"/>
       <c r="C13" s="47" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E13" s="47">
         <v>0</v>
       </c>
       <c r="F13" s="47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -22297,73 +22111,73 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:23">
       <c r="A1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D1" t="s">
         <v>287</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>288</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>289</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>290</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>291</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>292</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" s="31" t="s">
         <v>294</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>295</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="M1" t="s">
         <v>296</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="N1" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>298</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>299</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="Q1" t="s">
         <v>300</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>301</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" s="44" t="s">
         <v>303</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>304</v>
       </c>
-      <c r="S1" s="45" t="s">
+      <c r="V1" t="s">
         <v>305</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="W1" t="s">
         <v>306</v>
-      </c>
-      <c r="U1" t="s">
-        <v>307</v>
-      </c>
-      <c r="V1" t="s">
-        <v>308</v>
-      </c>
-      <c r="W1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:23">
@@ -22371,56 +22185,56 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E2" t="s">
         <v>310</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>311</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>312</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>313</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>314</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="L2" t="s">
         <v>316</v>
       </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>317</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="L2" t="s">
-        <v>319</v>
-      </c>
-      <c r="M2" t="s">
-        <v>320</v>
       </c>
       <c r="N2" s="31" t="e">
         <f>_xlfn.XLOOKUP(K2,资产表!C:C,资产表!AG:AG,“”)</f>
         <v>#NAME?</v>
       </c>
       <c r="O2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q2" t="s">
+        <v>317</v>
+      </c>
+      <c r="R2" t="s">
         <v>320</v>
-      </c>
-      <c r="R2" t="s">
-        <v>323</v>
       </c>
       <c r="S2" s="44">
         <v>45513.0042476852</v>
@@ -22429,13 +22243,13 @@
         <v>46004.017974537</v>
       </c>
       <c r="U2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="V2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="W2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:23">
@@ -22443,56 +22257,56 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E3" t="s">
         <v>310</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>311</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>312</v>
       </c>
-      <c r="E3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I3" t="s">
         <v>314</v>
       </c>
-      <c r="G3" t="s">
-        <v>315</v>
-      </c>
-      <c r="H3" t="s">
-        <v>327</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" s="31" t="s">
+        <v>325</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>325</v>
+      </c>
+      <c r="L3" t="s">
+        <v>316</v>
+      </c>
+      <c r="M3" t="s">
         <v>317</v>
-      </c>
-      <c r="J3" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="K3" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="L3" t="s">
-        <v>319</v>
-      </c>
-      <c r="M3" t="s">
-        <v>320</v>
       </c>
       <c r="N3" s="31" t="e">
         <f>_xlfn.XLOOKUP(K3,资产表!C:C,资产表!AG:AG,“”)</f>
         <v>#NAME?</v>
       </c>
       <c r="O3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q3" t="s">
+        <v>317</v>
+      </c>
+      <c r="R3" t="s">
         <v>320</v>
-      </c>
-      <c r="R3" t="s">
-        <v>323</v>
       </c>
       <c r="S3" s="44">
         <v>45513.0042476852</v>
@@ -22501,13 +22315,13 @@
         <v>46004.0191435185</v>
       </c>
       <c r="U3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="V3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="W3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:23">
@@ -22515,56 +22329,56 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F4" t="s">
+        <v>311</v>
+      </c>
+      <c r="G4" t="s">
+        <v>312</v>
+      </c>
+      <c r="H4" t="s">
         <v>329</v>
       </c>
-      <c r="C4" t="s">
+      <c r="I4" t="s">
+        <v>314</v>
+      </c>
+      <c r="J4" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="D4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="K4" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="L4" t="s">
         <v>331</v>
       </c>
-      <c r="F4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G4" t="s">
-        <v>315</v>
-      </c>
-      <c r="H4" t="s">
-        <v>332</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="M4" t="s">
         <v>317</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="L4" t="s">
-        <v>334</v>
-      </c>
-      <c r="M4" t="s">
-        <v>320</v>
       </c>
       <c r="N4" s="31" t="e">
         <f>_xlfn.XLOOKUP(K4,资产表!C:C,资产表!AG:AG,“”)</f>
         <v>#NAME?</v>
       </c>
       <c r="O4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q4" t="s">
+        <v>317</v>
+      </c>
+      <c r="R4" t="s">
         <v>320</v>
-      </c>
-      <c r="R4" t="s">
-        <v>323</v>
       </c>
       <c r="S4" s="44">
         <v>45513.0050578704</v>
@@ -22573,13 +22387,13 @@
         <v>46004.018587963</v>
       </c>
       <c r="U4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="V4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="W4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:23">
@@ -22587,56 +22401,56 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D5" t="s">
+        <v>309</v>
+      </c>
+      <c r="E5" t="s">
+        <v>328</v>
+      </c>
+      <c r="F5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G5" t="s">
         <v>312</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
+        <v>336</v>
+      </c>
+      <c r="I5" t="s">
+        <v>314</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="L5" t="s">
         <v>331</v>
       </c>
-      <c r="F5" t="s">
-        <v>314</v>
-      </c>
-      <c r="G5" t="s">
-        <v>315</v>
-      </c>
-      <c r="H5" t="s">
-        <v>339</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="M5" t="s">
         <v>317</v>
-      </c>
-      <c r="J5" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="K5" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="L5" t="s">
-        <v>334</v>
-      </c>
-      <c r="M5" t="s">
-        <v>320</v>
       </c>
       <c r="N5" s="31" t="e">
         <f>_xlfn.XLOOKUP(K5,资产表!C:C,资产表!AG:AG,“”)</f>
         <v>#NAME?</v>
       </c>
       <c r="O5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q5" t="s">
+        <v>317</v>
+      </c>
+      <c r="R5" t="s">
         <v>320</v>
-      </c>
-      <c r="R5" t="s">
-        <v>323</v>
       </c>
       <c r="S5" s="44">
         <v>45513.0051736111</v>
@@ -22645,13 +22459,13 @@
         <v>46004.0177893518</v>
       </c>
       <c r="U5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="V5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="W5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:23">
@@ -22659,56 +22473,56 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E6" t="s">
+        <v>339</v>
+      </c>
+      <c r="F6" t="s">
+        <v>311</v>
+      </c>
+      <c r="G6" t="s">
+        <v>312</v>
+      </c>
+      <c r="H6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I6" t="s">
+        <v>314</v>
+      </c>
+      <c r="J6" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="D6" t="s">
-        <v>312</v>
-      </c>
-      <c r="E6" t="s">
-        <v>342</v>
-      </c>
-      <c r="F6" t="s">
-        <v>314</v>
-      </c>
-      <c r="G6" t="s">
-        <v>315</v>
-      </c>
-      <c r="H6" t="s">
-        <v>343</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="K6" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="L6" t="s">
+        <v>331</v>
+      </c>
+      <c r="M6" t="s">
         <v>317</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="K6" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="L6" t="s">
-        <v>334</v>
-      </c>
-      <c r="M6" t="s">
-        <v>320</v>
       </c>
       <c r="N6" s="31" t="e">
         <f>_xlfn.XLOOKUP(K6,资产表!C:C,资产表!AG:AG,“”)</f>
         <v>#NAME?</v>
       </c>
       <c r="O6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q6" t="s">
+        <v>317</v>
+      </c>
+      <c r="R6" t="s">
         <v>320</v>
-      </c>
-      <c r="R6" t="s">
-        <v>323</v>
       </c>
       <c r="S6" s="44">
         <v>45513.0049305556</v>
@@ -22717,13 +22531,13 @@
         <v>46004.018587963</v>
       </c>
       <c r="U6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="V6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="W6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:23">
@@ -22731,56 +22545,56 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E7" t="s">
+        <v>339</v>
+      </c>
+      <c r="F7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G7" t="s">
         <v>312</v>
       </c>
-      <c r="E7" t="s">
-        <v>342</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
+        <v>344</v>
+      </c>
+      <c r="I7" t="s">
         <v>314</v>
       </c>
-      <c r="G7" t="s">
-        <v>315</v>
-      </c>
-      <c r="H7" t="s">
-        <v>347</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="L7" t="s">
+        <v>331</v>
+      </c>
+      <c r="M7" t="s">
         <v>317</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="K7" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="L7" t="s">
-        <v>334</v>
-      </c>
-      <c r="M7" t="s">
-        <v>320</v>
       </c>
       <c r="N7" s="31" t="e">
         <f>_xlfn.XLOOKUP(K7,资产表!C:C,资产表!AG:AG,“”)</f>
         <v>#NAME?</v>
       </c>
       <c r="O7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q7" t="s">
+        <v>317</v>
+      </c>
+      <c r="R7" t="s">
         <v>320</v>
-      </c>
-      <c r="R7" t="s">
-        <v>323</v>
       </c>
       <c r="S7" s="44">
         <v>45513.0050578704</v>
@@ -22789,13 +22603,13 @@
         <v>46004.0186226852</v>
       </c>
       <c r="U7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="V7" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="W7" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:23">
@@ -22803,56 +22617,56 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C8" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" t="s">
+        <v>339</v>
+      </c>
+      <c r="F8" t="s">
+        <v>311</v>
+      </c>
+      <c r="G8" t="s">
         <v>312</v>
       </c>
-      <c r="E8" t="s">
-        <v>342</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
+        <v>347</v>
+      </c>
+      <c r="I8" t="s">
         <v>314</v>
       </c>
-      <c r="G8" t="s">
-        <v>315</v>
-      </c>
-      <c r="H8" t="s">
-        <v>350</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="J8" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="L8" t="s">
+        <v>331</v>
+      </c>
+      <c r="M8" t="s">
         <v>317</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="K8" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="L8" t="s">
-        <v>334</v>
-      </c>
-      <c r="M8" t="s">
-        <v>320</v>
       </c>
       <c r="N8" s="31" t="e">
         <f>_xlfn.XLOOKUP(K8,资产表!C:C,资产表!AG:AG,“”)</f>
         <v>#NAME?</v>
       </c>
       <c r="O8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q8" t="s">
+        <v>317</v>
+      </c>
+      <c r="R8" t="s">
         <v>320</v>
-      </c>
-      <c r="R8" t="s">
-        <v>323</v>
       </c>
       <c r="S8" s="44">
         <v>45513.0051736111</v>
@@ -22861,13 +22675,13 @@
         <v>46004.0177893518</v>
       </c>
       <c r="U8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="V8" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="W8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:23">
@@ -22875,56 +22689,56 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D9" t="s">
+        <v>309</v>
+      </c>
+      <c r="E9" t="s">
+        <v>339</v>
+      </c>
+      <c r="F9" t="s">
+        <v>311</v>
+      </c>
+      <c r="G9" t="s">
         <v>312</v>
       </c>
-      <c r="E9" t="s">
-        <v>342</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
+        <v>351</v>
+      </c>
+      <c r="I9" t="s">
         <v>314</v>
       </c>
-      <c r="G9" t="s">
-        <v>315</v>
-      </c>
-      <c r="H9" t="s">
-        <v>354</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="J9" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="L9" t="s">
+        <v>331</v>
+      </c>
+      <c r="M9" t="s">
         <v>317</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="L9" t="s">
-        <v>334</v>
-      </c>
-      <c r="M9" t="s">
-        <v>320</v>
       </c>
       <c r="N9" s="31" t="e">
         <f>_xlfn.XLOOKUP(K9,资产表!C:C,资产表!AG:AG,“”)</f>
         <v>#NAME?</v>
       </c>
       <c r="O9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q9" t="s">
+        <v>317</v>
+      </c>
+      <c r="R9" t="s">
         <v>320</v>
-      </c>
-      <c r="R9" t="s">
-        <v>323</v>
       </c>
       <c r="S9" s="44">
         <v>45513.0061574074</v>
@@ -22933,13 +22747,13 @@
         <v>46004.0177893518</v>
       </c>
       <c r="U9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="V9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="W9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -22981,112 +22795,112 @@
   <sheetData>
     <row r="1" s="29" customFormat="1" ht="24" spans="1:36">
       <c r="A1" s="33" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B1" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="E1" s="34" t="s">
         <v>355</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="F1" s="35" t="s">
         <v>356</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="G1" s="33" t="s">
         <v>357</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="H1" s="33" t="s">
         <v>358</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="I1" s="33" t="s">
         <v>359</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="J1" s="33" t="s">
         <v>360</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="K1" s="33" t="s">
         <v>361</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="L1" s="33" t="s">
         <v>362</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="M1" s="33" t="s">
         <v>363</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="N1" s="33" t="s">
         <v>364</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="O1" s="33" t="s">
         <v>365</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="P1" s="33" t="s">
         <v>366</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="Q1" s="33" t="s">
         <v>367</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="R1" s="33" t="s">
         <v>368</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="S1" s="33" t="s">
         <v>369</v>
       </c>
-      <c r="Q1" s="33" t="s">
+      <c r="T1" s="33" t="s">
         <v>370</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="U1" s="33" t="s">
         <v>371</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="V1" s="33" t="s">
         <v>372</v>
       </c>
-      <c r="T1" s="33" t="s">
+      <c r="W1" s="33" t="s">
         <v>373</v>
       </c>
-      <c r="U1" s="33" t="s">
+      <c r="X1" s="33" t="s">
         <v>374</v>
       </c>
-      <c r="V1" s="33" t="s">
+      <c r="Y1" s="33" t="s">
         <v>375</v>
       </c>
-      <c r="W1" s="33" t="s">
+      <c r="Z1" s="33" t="s">
         <v>376</v>
       </c>
-      <c r="X1" s="33" t="s">
+      <c r="AA1" s="33" t="s">
         <v>377</v>
       </c>
-      <c r="Y1" s="33" t="s">
+      <c r="AB1" s="33" t="s">
         <v>378</v>
       </c>
-      <c r="Z1" s="33" t="s">
+      <c r="AC1" s="33" t="s">
         <v>379</v>
       </c>
-      <c r="AA1" s="33" t="s">
+      <c r="AD1" s="33" t="s">
         <v>380</v>
       </c>
-      <c r="AB1" s="33" t="s">
+      <c r="AE1" s="33" t="s">
         <v>381</v>
       </c>
-      <c r="AC1" s="33" t="s">
+      <c r="AF1" s="33" t="s">
         <v>382</v>
       </c>
-      <c r="AD1" s="33" t="s">
+      <c r="AG1" s="36" t="s">
         <v>383</v>
       </c>
-      <c r="AE1" s="33" t="s">
+      <c r="AH1" s="33" t="s">
         <v>384</v>
       </c>
-      <c r="AF1" s="33" t="s">
+      <c r="AI1" s="37" t="s">
         <v>385</v>
       </c>
-      <c r="AG1" s="36" t="s">
+      <c r="AJ1" s="37" t="s">
         <v>386</v>
-      </c>
-      <c r="AH1" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="AI1" s="37" t="s">
-        <v>388</v>
-      </c>
-      <c r="AJ1" s="37" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="2" s="30" customFormat="1" spans="1:36">
@@ -23094,46 +22908,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E2" s="38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F2" s="40" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G2" s="41"/>
       <c r="H2" s="41"/>
       <c r="I2" s="41"/>
       <c r="J2" s="41"/>
       <c r="K2" s="38" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L2" s="41"/>
       <c r="M2" s="38" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="N2" s="38" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O2" s="41"/>
       <c r="P2" s="38" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="Q2" s="41"/>
       <c r="R2" s="38" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="S2" s="41"/>
       <c r="T2" s="41"/>
       <c r="U2" s="41"/>
       <c r="V2" s="41"/>
       <c r="W2" s="38" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="X2" s="41"/>
       <c r="Y2" s="41"/>
@@ -23145,7 +22959,7 @@
       <c r="AE2" s="41"/>
       <c r="AF2" s="41"/>
       <c r="AG2" s="42" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AH2" s="41"/>
       <c r="AI2" s="41"/>
@@ -23156,37 +22970,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>6</v>
+        <v>398</v>
       </c>
       <c r="C3" s="38"/>
       <c r="D3" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
       <c r="I3" s="43"/>
       <c r="J3" s="43"/>
       <c r="K3" s="38" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L3" s="43"/>
       <c r="M3" s="38" t="s">
+        <v>400</v>
+      </c>
+      <c r="N3" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="O3" s="38" t="s">
         <v>402</v>
       </c>
-      <c r="N3" s="38" t="s">
+      <c r="P3" s="38" t="s">
         <v>403</v>
-      </c>
-      <c r="O3" s="38" t="s">
-        <v>404</v>
-      </c>
-      <c r="P3" s="38" t="s">
-        <v>405</v>
       </c>
       <c r="Q3" s="43"/>
       <c r="R3" s="43"/>
@@ -23195,7 +23009,7 @@
       <c r="U3" s="43"/>
       <c r="V3" s="43"/>
       <c r="W3" s="38" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="X3" s="43"/>
       <c r="Y3" s="43"/>
@@ -23207,7 +23021,7 @@
       <c r="AE3" s="43"/>
       <c r="AF3" s="43"/>
       <c r="AG3" s="42" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AH3" s="43"/>
       <c r="AI3" s="43"/>
@@ -23218,31 +23032,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>6</v>
+        <v>398</v>
       </c>
       <c r="C4" s="38"/>
       <c r="D4" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G4" s="43"/>
       <c r="H4" s="43"/>
       <c r="I4" s="43"/>
       <c r="J4" s="43"/>
       <c r="K4" s="38" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L4" s="43"/>
       <c r="M4" s="38" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="N4" s="38" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O4" s="43"/>
       <c r="P4" s="43"/>
@@ -23263,7 +23077,7 @@
       <c r="AE4" s="43"/>
       <c r="AF4" s="43"/>
       <c r="AG4" s="42" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AH4" s="43"/>
       <c r="AI4" s="43"/>
@@ -23274,35 +23088,35 @@
         <v>4</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>12</v>
+        <v>407</v>
       </c>
       <c r="C5" s="38"/>
       <c r="D5" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G5" s="43"/>
       <c r="H5" s="43"/>
       <c r="I5" s="43"/>
       <c r="J5" s="43"/>
       <c r="K5" s="38" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L5" s="43"/>
       <c r="M5" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N5" s="38" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O5" s="43"/>
       <c r="P5" s="38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q5" s="43"/>
       <c r="R5" s="43"/>
@@ -23311,11 +23125,11 @@
       <c r="U5" s="43"/>
       <c r="V5" s="43"/>
       <c r="W5" s="38" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="X5" s="43"/>
       <c r="Y5" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z5" s="43"/>
       <c r="AA5" s="43"/>
@@ -23325,7 +23139,7 @@
       <c r="AE5" s="43"/>
       <c r="AF5" s="43"/>
       <c r="AG5" s="42" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AH5" s="43"/>
       <c r="AI5" s="43"/>
@@ -23336,29 +23150,29 @@
         <v>5</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>12</v>
+        <v>407</v>
       </c>
       <c r="C6" s="38"/>
       <c r="D6" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G6" s="43"/>
       <c r="H6" s="43"/>
       <c r="I6" s="43"/>
       <c r="J6" s="43"/>
       <c r="K6" s="38" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L6" s="43"/>
       <c r="M6" s="43"/>
       <c r="N6" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O6" s="43"/>
       <c r="P6" s="43"/>
@@ -23379,7 +23193,7 @@
       <c r="AE6" s="43"/>
       <c r="AF6" s="43"/>
       <c r="AG6" s="42" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AH6" s="43"/>
       <c r="AI6" s="43"/>
@@ -23390,29 +23204,29 @@
         <v>6</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>12</v>
+        <v>407</v>
       </c>
       <c r="C7" s="38"/>
       <c r="D7" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G7" s="43"/>
       <c r="H7" s="43"/>
       <c r="I7" s="43"/>
       <c r="J7" s="43"/>
       <c r="K7" s="38" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L7" s="43"/>
       <c r="M7" s="43"/>
       <c r="N7" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O7" s="43"/>
       <c r="P7" s="43"/>
@@ -23433,7 +23247,7 @@
       <c r="AE7" s="43"/>
       <c r="AF7" s="43"/>
       <c r="AG7" s="42" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AH7" s="43"/>
       <c r="AI7" s="43"/>
@@ -23444,29 +23258,29 @@
         <v>7</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>17</v>
+        <v>413</v>
       </c>
       <c r="C8" s="38"/>
       <c r="D8" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G8" s="43"/>
       <c r="H8" s="43"/>
       <c r="I8" s="43"/>
       <c r="J8" s="43"/>
       <c r="K8" s="38" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L8" s="43"/>
       <c r="M8" s="43"/>
       <c r="N8" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O8" s="43"/>
       <c r="P8" s="43"/>
@@ -23487,7 +23301,7 @@
       <c r="AE8" s="43"/>
       <c r="AF8" s="43"/>
       <c r="AG8" s="42" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AH8" s="43"/>
       <c r="AI8" s="43"/>
@@ -23498,29 +23312,29 @@
         <v>8</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>17</v>
+        <v>413</v>
       </c>
       <c r="C9" s="38"/>
       <c r="D9" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E9" s="38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G9" s="43"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
       <c r="J9" s="43"/>
       <c r="K9" s="38" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L9" s="43"/>
       <c r="M9" s="43"/>
       <c r="N9" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O9" s="43"/>
       <c r="P9" s="43"/>
@@ -23541,7 +23355,7 @@
       <c r="AE9" s="43"/>
       <c r="AF9" s="43"/>
       <c r="AG9" s="42" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AH9" s="43"/>
       <c r="AI9" s="43"/>
@@ -23552,31 +23366,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>17</v>
+        <v>413</v>
       </c>
       <c r="C10" s="38"/>
       <c r="D10" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G10" s="43"/>
       <c r="H10" s="43"/>
       <c r="I10" s="43"/>
       <c r="J10" s="43"/>
       <c r="K10" s="38" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L10" s="43"/>
       <c r="M10" s="38" t="s">
         <v>414</v>
       </c>
       <c r="N10" s="38" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="O10" s="43"/>
       <c r="P10" s="43"/>
@@ -23597,7 +23411,7 @@
       <c r="AE10" s="43"/>
       <c r="AF10" s="43"/>
       <c r="AG10" s="42" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AH10" s="43"/>
       <c r="AI10" s="43"/>
@@ -23846,7 +23660,7 @@
         <v>473</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X2" s="26" t="s">
         <v>474</v>
@@ -23953,7 +23767,7 @@
         <v>473</v>
       </c>
       <c r="W3" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X3" s="26" t="s">
         <v>474</v>
@@ -24068,7 +23882,7 @@
         <v>473</v>
       </c>
       <c r="W4" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X4" s="26" t="s">
         <v>474</v>
@@ -24179,7 +23993,7 @@
         <v>473</v>
       </c>
       <c r="W5" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X5" s="26" t="s">
         <v>474</v>
@@ -24283,10 +24097,10 @@
         <v>518</v>
       </c>
       <c r="V6" s="26" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="W6" s="26" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="X6" s="26" t="s">
         <v>519</v>
@@ -24399,7 +24213,7 @@
         <v>473</v>
       </c>
       <c r="W7" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X7" s="26" t="s">
         <v>474</v>
@@ -24514,7 +24328,7 @@
         <v>473</v>
       </c>
       <c r="W8" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X8" s="26" t="s">
         <v>474</v>
@@ -24625,7 +24439,7 @@
         <v>473</v>
       </c>
       <c r="W9" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X9" s="26" t="s">
         <v>474</v>
@@ -24736,7 +24550,7 @@
         <v>473</v>
       </c>
       <c r="W10" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X10" s="26" t="s">
         <v>474</v>
@@ -24843,7 +24657,7 @@
         <v>473</v>
       </c>
       <c r="W11" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X11" s="26" t="s">
         <v>474</v>
@@ -24954,7 +24768,7 @@
         <v>473</v>
       </c>
       <c r="W12" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X12" s="26" t="s">
         <v>474</v>
@@ -25065,7 +24879,7 @@
         <v>473</v>
       </c>
       <c r="W13" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X13" s="26" t="s">
         <v>474</v>
@@ -25176,7 +24990,7 @@
         <v>473</v>
       </c>
       <c r="W14" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X14" s="26" t="s">
         <v>474</v>
@@ -25295,13 +25109,13 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="24" customHeight="1" spans="1:56">
       <c r="A2" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>542</v>
@@ -25310,7 +25124,7 @@
         <v>417</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>432</v>
@@ -25343,7 +25157,7 @@
         <v>548</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="R2" s="12" t="s">
         <v>549</v>
@@ -25373,7 +25187,7 @@
         <v>436</v>
       </c>
       <c r="AA2" s="12" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AB2" s="12" t="s">
         <v>433</v>
@@ -25691,13 +25505,13 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:56">
       <c r="A5" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B5" s="2">
         <v>45947.364375</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>499</v>
@@ -25718,7 +25532,7 @@
         <v>588</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O5" s="17" t="s">
         <v>485</v>
@@ -25730,7 +25544,7 @@
         <v>475</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="U5" s="15"/>
       <c r="V5" s="18" t="s">
@@ -25811,7 +25625,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:56">
       <c r="A6" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B6" s="2">
         <v>45973.5874768519</v>
@@ -25838,7 +25652,7 @@
         <v>588</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O6" s="17" t="s">
         <v>485</v>
@@ -25850,7 +25664,7 @@
         <v>475</v>
       </c>
       <c r="T6" s="15" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="U6" s="15"/>
       <c r="V6" s="18" t="s">
@@ -25933,7 +25747,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:56">
       <c r="A7" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B7" s="2">
         <v>46076.7486689815</v>
@@ -25972,7 +25786,7 @@
         <v>475</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="U7" s="15"/>
       <c r="V7" s="18" t="s">
@@ -26059,7 +25873,7 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:56">
       <c r="A8" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B8" s="2">
         <v>46077.6402662037</v>
@@ -26082,13 +25896,13 @@
       </c>
       <c r="K8" s="15"/>
       <c r="L8" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M8" s="15" t="s">
         <v>588</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O8" s="17" t="s">
         <v>485</v>
@@ -26100,7 +25914,7 @@
         <v>475</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="U8" s="15"/>
       <c r="V8" s="18" t="s">
@@ -26185,7 +25999,7 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:56">
       <c r="A9" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B9" s="2">
         <v>45985.3865509259</v>
@@ -26311,7 +26125,7 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:56">
       <c r="A10" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B10" s="2">
         <v>45880.4008564815</v>
@@ -26350,7 +26164,7 @@
         <v>475</v>
       </c>
       <c r="T10" s="15" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="U10" s="15"/>
       <c r="V10" s="20" t="s">
@@ -26437,7 +26251,7 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:56">
       <c r="A11" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B11" s="2">
         <v>45958.7312037037</v>
@@ -26476,7 +26290,7 @@
         <v>475</v>
       </c>
       <c r="T11" s="15" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="U11" s="15"/>
       <c r="V11" s="22" t="s">
@@ -26563,13 +26377,13 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:56">
       <c r="A12" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B12" s="2">
         <v>45870.6352777778</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>617</v>
@@ -26586,13 +26400,13 @@
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M12" s="15" t="s">
         <v>588</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="O12" s="17" t="s">
         <v>485</v>
@@ -26616,7 +26430,7 @@
       </c>
       <c r="Y12" s="15"/>
       <c r="Z12" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AA12" s="15"/>
       <c r="AB12" s="15"/>
@@ -26685,13 +26499,13 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:56">
       <c r="A13" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B13" s="2">
         <v>45871.5828819444</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>617</v>
@@ -26708,13 +26522,13 @@
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>588</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="O13" s="21" t="s">
         <v>485</v>
@@ -26738,7 +26552,7 @@
       </c>
       <c r="Y13" s="15"/>
       <c r="Z13" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AA13" s="15"/>
       <c r="AB13" s="15"/>
@@ -26807,7 +26621,7 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:56">
       <c r="A14" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B14" s="2">
         <v>46059.4420949074</v>
@@ -26856,7 +26670,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="15"/>
       <c r="Z14" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AA14" s="15"/>
       <c r="AB14" s="15"/>
@@ -26921,7 +26735,7 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:56">
       <c r="A15" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B15" s="2">
         <v>46059.6016087963</v>
@@ -26970,7 +26784,7 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="15"/>
       <c r="Z15" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AA15" s="15"/>
       <c r="AB15" s="15"/>
@@ -27035,7 +26849,7 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:56">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B16" s="2">
         <v>46079.6532638889</v>
@@ -27084,7 +26898,7 @@
       <c r="X16" s="15"/>
       <c r="Y16" s="15"/>
       <c r="Z16" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AA16" s="15"/>
       <c r="AB16" s="15"/>
@@ -27149,7 +26963,7 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:56">
       <c r="A17" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B17" s="2">
         <v>46086.4138657407</v>
@@ -27198,7 +27012,7 @@
       <c r="X17" s="15"/>
       <c r="Y17" s="15"/>
       <c r="Z17" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AA17" s="15"/>
       <c r="AB17" s="15"/>
@@ -27263,7 +27077,7 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:56">
       <c r="A18" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B18" s="2">
         <v>46090.5363888889</v>
@@ -27286,7 +27100,7 @@
       </c>
       <c r="K18" s="15"/>
       <c r="L18" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M18" s="15" t="s">
         <v>588</v>
@@ -27304,7 +27118,7 @@
         <v>475</v>
       </c>
       <c r="T18" s="15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="U18" s="15"/>
       <c r="V18" s="18" t="s">
@@ -27389,7 +27203,7 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:56">
       <c r="A19" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B19" s="2">
         <v>46091.6809953704</v>
@@ -27438,7 +27252,7 @@
       <c r="X19" s="15"/>
       <c r="Y19" s="15"/>
       <c r="Z19" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AA19" s="15"/>
       <c r="AB19" s="15"/>
@@ -27503,7 +27317,7 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:56">
       <c r="A20" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B20" s="2">
         <v>46094.6038888889</v>
@@ -27552,7 +27366,7 @@
       <c r="X20" s="15"/>
       <c r="Y20" s="15"/>
       <c r="Z20" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AA20" s="15"/>
       <c r="AB20" s="15"/>

--- a/mss_ai_ppt_sample_assets/backend/data/plus_data.xlsx
+++ b/mss_ai_ppt_sample_assets/backend/data/plus_data.xlsx
@@ -19392,7 +19392,7 @@
       </c>
       <c r="I1" s="115">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
